--- a/cache/resid_sepidar_template.xlsx
+++ b/cache/resid_sepidar_template.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\milad\Desktop\milad_repo\cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02D30706-A4C8-4EE5-BDF3-8B0467214532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BCF9634-0FBD-41C3-A680-628780B34891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="6315" windowWidth="21600" windowHeight="11385" xr2:uid="{3D4B2A58-54A8-4AE8-A1F5-94B26AA454D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{83EEF9FF-486E-45B8-B529-E2369E6CE5FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Test" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>نوع قلم</t>
   </si>
@@ -49,9 +49,57 @@
     <t>رسيد دريافت شرح</t>
   </si>
   <si>
+    <t>رسيد دريافت شرح(2)</t>
+  </si>
+  <si>
     <t>رسيد دريافت حساب معين</t>
   </si>
   <si>
+    <t>چك شماره</t>
+  </si>
+  <si>
+    <t>چك پشت نمره</t>
+  </si>
+  <si>
+    <t>چك مبلغ</t>
+  </si>
+  <si>
+    <t>چك تاريخ سررسيد</t>
+  </si>
+  <si>
+    <t>چك بانك</t>
+  </si>
+  <si>
+    <t>چك كد شعبه</t>
+  </si>
+  <si>
+    <t>چك شعبه1</t>
+  </si>
+  <si>
+    <t>چك شماره حساب</t>
+  </si>
+  <si>
+    <t>چك شرح</t>
+  </si>
+  <si>
+    <t>چك شرح (2)</t>
+  </si>
+  <si>
+    <t>چك بانك(2)</t>
+  </si>
+  <si>
+    <t>چك وضعيت استقرار</t>
+  </si>
+  <si>
+    <t>چك تاريخ واگذاري</t>
+  </si>
+  <si>
+    <t>چك شماره واگذاري</t>
+  </si>
+  <si>
+    <t>چك حساب بانكي واگذاري</t>
+  </si>
+  <si>
     <t xml:space="preserve">رسيد دريافت مبلغ دريافت </t>
   </si>
   <si>
@@ -70,19 +118,25 @@
     <t>حواله شرح</t>
   </si>
   <si>
+    <t>حواله شرح(2)</t>
+  </si>
+  <si>
     <t>حواله تفصيل حساب بانكي</t>
   </si>
   <si>
+    <t>كارت خوان شماره ترمينال</t>
+  </si>
+  <si>
+    <t>كارت خوان حساب بانكي</t>
+  </si>
+  <si>
+    <t>كارت خوان مبلغ</t>
+  </si>
+  <si>
     <t>رسيد دريافت تخفيف</t>
   </si>
   <si>
     <t>رسيد دريافت استقراري</t>
-  </si>
-  <si>
-    <t>رسيد دريافت كد</t>
-  </si>
-  <si>
-    <t>رسيد دريافت نوع آيتم</t>
   </si>
 </sst>
 </file>
@@ -99,7 +153,7 @@
       <name val="Tahoma"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,6 +163,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -125,9 +185,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,8 +522,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4825518-01F8-464E-A3E5-64E4B1EEC9A5}">
-  <dimension ref="A1:U1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A653A9A-9A2C-4286-99FC-E4FC594932F8}">
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -470,20 +531,23 @@
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="45.28515625" customWidth="1"/>
-    <col min="9" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="20" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="20" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="20" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="10" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" bestFit="1" customWidth="1"/>
+    <col min="31" max="36" width="20" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="13" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,6 +611,306 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+    </row>
+    <row r="3" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+      <c r="AH4" s="2"/>
+      <c r="AI4" s="2"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AL4" s="2"/>
+      <c r="AM4" s="2"/>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="2"/>
+      <c r="AI6" s="2"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AL6" s="2"/>
+      <c r="AM6" s="2"/>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
